--- a/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
@@ -441,1102 +441,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.948954019821675e-06</v>
+        <v>0.01210362052016088</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.07287040295199387</v>
+        <v>-0.1137027707260424</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07127601824142453</v>
+        <v>0.04431962050523962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8.17103502819192e-08</v>
+        <v>0.1999586817892291</v>
       </c>
       <c r="B3" t="n">
-        <v>2.919555001828521e-09</v>
+        <v>-0.1680874484078807</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03996364765639992</v>
+        <v>-0.07392020685380714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.2154206274412335</v>
+        <v>0.216274209584133</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.06848075664894106</v>
+        <v>0.1449243335393811</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01961781746871145</v>
+        <v>-0.02666241010495472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.04156005722603636</v>
+        <v>-0.2461101646292367</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08293079693182412</v>
+        <v>-0.1206072214582163</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.562392365674606e-06</v>
+        <v>-0.1014415185692277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.01802878963902173</v>
+        <v>0.1845415960062787</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.07031709720800745</v>
+        <v>-0.03716442132934806</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1154612680682498</v>
+        <v>0.2063636095581707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0278076933794086</v>
+        <v>0.004820902716201437</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.001018990394661722</v>
+        <v>-0.01767585065248328</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.06300404849884705</v>
+        <v>0.1984348318495678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.03278201565498585</v>
+        <v>-0.08546171060641421</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2339939359259438</v>
+        <v>0.05064191794078829</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1036476842462081</v>
+        <v>-0.2253128665136343</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.03092169457784737</v>
+        <v>-0.1311979724010757</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1229900796749328</v>
+        <v>-0.1599795779034408</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1342160867801555</v>
+        <v>0.0760439515631898</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0886784609649709</v>
+        <v>0.1697832141461818</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1141982736598347</v>
+        <v>0.1849796649087322</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06478423538576125</v>
+        <v>0.04487144048295318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1392914920258337</v>
+        <v>0.1914108046034977</v>
       </c>
       <c r="B11" t="n">
-        <v>0.006473124162286914</v>
+        <v>0.08386734159945955</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2001651531520139</v>
+        <v>0.2069758950039365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.09468073344013125</v>
+        <v>0.000338740764926229</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.02627966847662963</v>
+        <v>-0.00184957119304665</v>
       </c>
       <c r="C12" t="n">
-        <v>0.007418503579177919</v>
+        <v>1.616123379022477e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0006688288926166314</v>
+        <v>0.03108737485621763</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.03318557655181574</v>
+        <v>0.08809787101598883</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.01054604505292646</v>
+        <v>-0.02928196792609933</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.04403368805664307</v>
+        <v>-0.02213007115215502</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1475922058984472</v>
+        <v>0.2149780466044623</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1192830653186049</v>
+        <v>0.04283862793902794</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.003938605393445312</v>
+        <v>0.01041097713150759</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0002346070859447945</v>
+        <v>-0.04113307066464365</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003122834673913675</v>
+        <v>0.02603502810783976</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.288375941135006e-06</v>
+        <v>0.2284795447213178</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0001075976104978688</v>
+        <v>0.2060769764788018</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.003798133040951539</v>
+        <v>0.2363338462699098</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.06324204122827878</v>
+        <v>0.05883648065591841</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03201080587896056</v>
+        <v>0.1912812101603729</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0005303358043887633</v>
+        <v>0.1743828315041423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.02019324010249648</v>
+        <v>0.1020598228169361</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.1545079115982534</v>
+        <v>-0.135163061487066</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1550033804894426</v>
+        <v>-0.2229992527193982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.009609877912882781</v>
+        <v>0.1691806569359391</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06382533487014691</v>
+        <v>0.1819050255118005</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1735502949905964</v>
+        <v>-0.06662914149083801</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1959010614614843</v>
+        <v>-0.1929522986084609</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.09502103752074509</v>
+        <v>-0.1324961413233522</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0768491290956006</v>
+        <v>-0.01108445305869458</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.1697677846339838</v>
+        <v>-0.2146412948326631</v>
       </c>
       <c r="B21" t="n">
-        <v>0.04817959746733134</v>
+        <v>0.01029032139743344</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1627825458683581</v>
+        <v>-0.05462453387676786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.2250503134325348</v>
+        <v>0.06402908137291642</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.05997782582081708</v>
+        <v>-9.617835626890516e-09</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1718704739138862</v>
+        <v>-0.2121664415655603</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1618564666765996</v>
+        <v>-0.03118660889159448</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.0495253874559146</v>
+        <v>-0.02845780906251944</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1884646155318804</v>
+        <v>-8.240560142102906e-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0123096578207831</v>
+        <v>0.09799395254223628</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.01513169083371843</v>
+        <v>0.08410061552557388</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1342591021004744</v>
+        <v>0.1655632402455098</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.08662383802792351</v>
+        <v>0.1754350546627619</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.2401026708827476</v>
+        <v>0.01033857368503461</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.06658596387368483</v>
+        <v>-0.005018535103430092</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.02652079073801693</v>
+        <v>-0.1486525030540925</v>
       </c>
       <c r="B26" t="n">
-        <v>0.07207329235846478</v>
+        <v>0.1340659120328411</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.07348291011305985</v>
+        <v>0.01814946479467297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.1975438323715328</v>
+        <v>-0.123175538477813</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.1509964037457551</v>
+        <v>0.1040434795361554</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1886454222506874</v>
+        <v>0.1289687993226445</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.00319165889390323</v>
+        <v>0.2333591323909409</v>
       </c>
       <c r="B28" t="n">
-        <v>-2.316069544765318e-06</v>
+        <v>-0.1359870752657822</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.01096625168088943</v>
+        <v>0.1706614395331824</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.1275136229876861</v>
+        <v>0.09466474842899737</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.2251025569019644</v>
+        <v>-0.1470731718993727</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.01421608559568173</v>
+        <v>-0.09675081967273866</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.1027637704791984</v>
+        <v>-0.03170187298491894</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.1343004376357824</v>
+        <v>-0.2246499371026885</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1836015872857214</v>
+        <v>-0.2065658858865287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.03904192001730159</v>
+        <v>-0.1666925976186634</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.158985448792978</v>
+        <v>-0.04707225553828176</v>
       </c>
       <c r="C31" t="n">
-        <v>0.124081093061848</v>
+        <v>-0.1179899482496636</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.02201395276553665</v>
+        <v>-0.09856269879864725</v>
       </c>
       <c r="B32" t="n">
-        <v>0.08871358222065219</v>
+        <v>0.1709930166147157</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06610170871056889</v>
+        <v>-0.09099499289440634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.04891709012998904</v>
+        <v>-0.01716643915916196</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.1636262456458796</v>
+        <v>-0.1469700746482046</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.165060006309772</v>
+        <v>0.1786035814518295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2414938251449196</v>
+        <v>0.05169602606667583</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.04292099455195036</v>
+        <v>0.1208591653029723</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2012970909074171</v>
+        <v>-0.1109202490538979</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.04329411997368061</v>
+        <v>-0.04227027272148021</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0002506531543310714</v>
+        <v>-0.1740056855807975</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.002317746661937147</v>
+        <v>-0.1462717563071722</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.01669853435076253</v>
+        <v>0.2314045316407442</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1238687770619944</v>
+        <v>-0.1505372735345572</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.07582799416464832</v>
+        <v>-0.2250700647577389</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.2425106872069113</v>
+        <v>-0.02168531968721452</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.07820148432030413</v>
+        <v>0.1023834965588014</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01949837625638064</v>
+        <v>-0.100227285822991</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.02705188565175259</v>
+        <v>0.06153236798329952</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2303432760040553</v>
+        <v>-0.2208413330737243</v>
       </c>
       <c r="C38" t="n">
-        <v>0.03595750760847514</v>
+        <v>0.2280601448740299</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.05813187331663393</v>
+        <v>0.2132747728486415</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.00437180759398396</v>
+        <v>0.2129255421798786</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1525193249830799</v>
+        <v>0.2328562500830196</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.1732327730143506</v>
+        <v>0.1234061178880579</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.09997756273200006</v>
+        <v>0.06552015940222125</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1916119571551581</v>
+        <v>0.137169766751453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.2019693747334038</v>
+        <v>-0.2046289038863549</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.05756237774348215</v>
+        <v>-0.2110806202892935</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.05324201174214914</v>
+        <v>-0.06853454396163873</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.08031671174446502</v>
+        <v>-0.1772067292850775</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2074714303053357</v>
+        <v>-0.1195752227907606</v>
       </c>
       <c r="C42" t="n">
-        <v>0.102786433781712</v>
+        <v>-0.143295155689667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.2101154269539979</v>
+        <v>0.07682625980587904</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.2265960099655783</v>
+        <v>0.006545432286438919</v>
       </c>
       <c r="C43" t="n">
-        <v>0.09897762590295919</v>
+        <v>0.04280840310651261</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.07123497753466312</v>
+        <v>-0.1615625357720086</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.2024936882216526</v>
+        <v>-0.1203654218029473</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.02262516799636514</v>
+        <v>-0.01484098613409475</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.0968727097112729</v>
+        <v>0.1812256191852517</v>
       </c>
       <c r="B45" t="n">
-        <v>0.220809816747282</v>
+        <v>-0.03027204388961807</v>
       </c>
       <c r="C45" t="n">
-        <v>0.121075018260189</v>
+        <v>-0.05782238279706713</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.1669216120095504</v>
+        <v>-0.1123354649118858</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.08390212700789297</v>
+        <v>-0.1401149507341461</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.08734060041683502</v>
+        <v>-0.05539843608296291</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.1423140776836357</v>
+        <v>5.141442444903261e-11</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.1717679271444481</v>
+        <v>5.237685760033048e-10</v>
       </c>
       <c r="C47" t="n">
-        <v>0.09656273884563554</v>
+        <v>-0.0006829735291770644</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.1898818340216773</v>
+        <v>0.001202000787823855</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.05950295182662205</v>
+        <v>0.001978699185609517</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2391247112569378</v>
+        <v>0.001167433080304127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.0008349291398918251</v>
+        <v>-0.1130988944704425</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.09450213913695875</v>
+        <v>0.1626980322383159</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.353639668255459e-07</v>
+        <v>0.01030629015914353</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.2052116507659519</v>
+        <v>-0.1715901962451064</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.1947553560069966</v>
+        <v>0.04611585041462059</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.05072181190955257</v>
+        <v>-0.1372587917139371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.1559135563624328</v>
+        <v>-0.1964583220901348</v>
       </c>
       <c r="B51" t="n">
-        <v>0.007431435842666131</v>
+        <v>-0.1679837971361418</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.07694323555404978</v>
+        <v>-0.02250437605027689</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.00103198912593006</v>
+        <v>0.1479201493849999</v>
       </c>
       <c r="B52" t="n">
-        <v>0.06588676041943894</v>
+        <v>-0.03104841588993119</v>
       </c>
       <c r="C52" t="n">
-        <v>0.09805780089652166</v>
+        <v>-0.07030894304916972</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.2138354434053395</v>
+        <v>0.2168494681952689</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.07583641682383517</v>
+        <v>-0.1382728908265186</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1077310101196755</v>
+        <v>-0.2221166518897794</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.06720637105542338</v>
+        <v>0.1168818084350754</v>
       </c>
       <c r="B54" t="n">
-        <v>0.05786945367288986</v>
+        <v>0.1542846748760279</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.03999860499584267</v>
+        <v>-0.1256576725063225</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.1562501678444803</v>
+        <v>0.07354511695087128</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0351197939633965</v>
+        <v>0.1671610952881677</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2215454741902183</v>
+        <v>-0.1456125947139978</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.01134700627033783</v>
+        <v>-0.1335289956808442</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0420036411873623</v>
+        <v>0.2276685738070083</v>
       </c>
       <c r="C56" t="n">
-        <v>0.05039103898296515</v>
+        <v>-0.04056744059968691</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.06935277508133877</v>
+        <v>0.01983890554358759</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0166515145018933</v>
+        <v>-0.2044939135950287</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1027194313915634</v>
+        <v>0.1747939948527393</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.003414965075214299</v>
+        <v>-0.06199898973498199</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.04969273707569045</v>
+        <v>0.1665649372224167</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1796773137682546</v>
+        <v>0.04057354755482517</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1537507777970067</v>
+        <v>0.1631920648567337</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1734759137092688</v>
+        <v>-0.1138971955549825</v>
       </c>
       <c r="C59" t="n">
-        <v>0.07406850111355036</v>
+        <v>-0.1278680228826398</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.2469552255175255</v>
+        <v>0.09093040783992744</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.2261527580757513</v>
+        <v>-0.1431356930028631</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.01933019978260794</v>
+        <v>0.1413816522145883</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.04216103205031494</v>
+        <v>-0.0001916000322994933</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.09357167817538284</v>
+        <v>0.01054401077734958</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.570157740336946e-07</v>
+        <v>1.153513763205981e-07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.1185521829465854</v>
+        <v>-0.101912970012308</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1023933751761419</v>
+        <v>0.1719446125746868</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1928011860514091</v>
+        <v>0.1994796716138168</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.04762734917523918</v>
+        <v>0.1140954834448455</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.07766827155882042</v>
+        <v>-0.05222123885022036</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.125376561006909</v>
+        <v>-0.08596579259932825</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.2141183652984748</v>
+        <v>-0.0001837166994705889</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1602782601316911</v>
+        <v>-0.02259890932793061</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1899592254145994</v>
+        <v>-0.04931176392208086</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.1191132169276046</v>
+        <v>-0.1155324207199708</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.0217810714684799</v>
+        <v>-0.2210733697617061</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.02582816829982739</v>
+        <v>0.2389200220527465</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.2298286993874959</v>
+        <v>0.1162765011008443</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.1858948031486496</v>
+        <v>0.05455831061465435</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1780327694164502</v>
+        <v>-0.04831438357741807</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.02821091287383362</v>
+        <v>0.02153841549610707</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.1052358083411412</v>
+        <v>0.08795533753134892</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.04716652374735995</v>
+        <v>0.1485925837878347</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.1875176227316935</v>
+        <v>-0.225341082227543</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1697364294298968</v>
+        <v>-0.02485002308670174</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0741358692243676</v>
+        <v>-0.002060242555181945</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.2343234548978863</v>
+        <v>0.1465120941399749</v>
       </c>
       <c r="B69" t="n">
-        <v>0.238650341739509</v>
+        <v>0.06579762640077647</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.150889611852429</v>
+        <v>-0.2320046470036324</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.1580757744135044</v>
+        <v>0.142971555039699</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1797111150100923</v>
+        <v>-0.07386487005547433</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1955939438440345</v>
+        <v>0.1407396158625648</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.08059631113327785</v>
+        <v>0.01211910382949168</v>
       </c>
       <c r="B71" t="n">
-        <v>0.08459716211647761</v>
+        <v>0.144457125867218</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2286093013091107</v>
+        <v>0.06220040081469529</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.1277171551872167</v>
+        <v>8.951193774234825e-07</v>
       </c>
       <c r="B72" t="n">
-        <v>0.04089225607879431</v>
+        <v>-0.0314484185481593</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2292760017605729</v>
+        <v>1.727502572750668e-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.03925821867130157</v>
+        <v>-5.313352468007647e-10</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1978727678276634</v>
+        <v>0.01986044868470015</v>
       </c>
       <c r="C73" t="n">
-        <v>0.156430118077809</v>
+        <v>8.513342831843539e-05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.2040618238781584</v>
+        <v>0.04288665411421533</v>
       </c>
       <c r="B74" t="n">
-        <v>0.2065790026176708</v>
+        <v>-0.09564388879223766</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.02471523046073082</v>
+        <v>-0.2092881621080661</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.1841825712344515</v>
+        <v>-1.122043559573601e-08</v>
       </c>
       <c r="B75" t="n">
-        <v>0.013457675851782</v>
+        <v>0.0008101374567341666</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0201883729082177</v>
+        <v>-0.01842463109439616</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.1423252282872722</v>
+        <v>0.150548741837869</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.1659466603365556</v>
+        <v>0.07955158755047434</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2165776424275511</v>
+        <v>0.2222822316750688</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.1580741011526611</v>
+        <v>6.07827306130887e-06</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1029757561889601</v>
+        <v>0.003877149729844037</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1232075923201409</v>
+        <v>0.001600234095611573</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.06815434563652892</v>
+        <v>0.07775929850822171</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.2270616919016069</v>
+        <v>0.1425104752694273</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1450205159508853</v>
+        <v>0.04141778599548119</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.1140692268108355</v>
+        <v>-0.1707879625765426</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1994640976506645</v>
+        <v>-0.1284983795817152</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1127704920528615</v>
+        <v>0.2059719953310357</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.07370641999080328</v>
+        <v>-0.001605108234900618</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1500653491677685</v>
+        <v>-0.01790301598523839</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1951921658417611</v>
+        <v>0.001844699051390847</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-0.1517253656285663</v>
+        <v>0.0005498147212081143</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.04748563450873281</v>
+        <v>-0.001234030286833605</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1024725318101729</v>
+        <v>-0.00286526477589508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.05442355757498873</v>
+        <v>-0.2434355753070539</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.1579899056997829</v>
+        <v>0.000534515010480052</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.117723219359438</v>
+        <v>0.01862058388525854</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.09175375718646386</v>
+        <v>0.2001218782566054</v>
       </c>
       <c r="B83" t="n">
-        <v>-4.849192190931403e-06</v>
+        <v>0.1712620472621791</v>
       </c>
       <c r="C83" t="n">
-        <v>0.006950563316248714</v>
+        <v>0.1367105003000828</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.1383481084656791</v>
+        <v>-0.1160139248092407</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1837937824898629</v>
+        <v>-0.1382412184791703</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.2395385542799409</v>
+        <v>0.1248792616613697</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.162079851897347</v>
+        <v>0.2091220682353377</v>
       </c>
       <c r="B85" t="n">
-        <v>0.05373212819568784</v>
+        <v>-0.02660210402539178</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2006127440489327</v>
+        <v>-0.08525320645153285</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.0270993520747058</v>
+        <v>8.801965675219919e-05</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.1456176899880822</v>
+        <v>-3.878540357103219e-05</v>
       </c>
       <c r="C86" t="n">
-        <v>0.09831173147337578</v>
+        <v>-0.007668642462300281</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.2182973590661831</v>
+        <v>-0.1121027669334636</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.02837804450579018</v>
+        <v>0.2289859706833824</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1097308417281311</v>
+        <v>-0.1318314112616442</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.1448817576013474</v>
+        <v>0.1584775369851397</v>
       </c>
       <c r="B88" t="n">
-        <v>0.01702528672951378</v>
+        <v>-0.155914349858095</v>
       </c>
       <c r="C88" t="n">
-        <v>0.06500818024940143</v>
+        <v>0.1683665080388387</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.0686165575412373</v>
+        <v>-0.01333229320358377</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.06315401424921344</v>
+        <v>-4.680805752566217e-05</v>
       </c>
       <c r="C89" t="n">
-        <v>0.09333763648781766</v>
+        <v>-0.01571014054063195</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.1235082943314015</v>
+        <v>0.227467040028459</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.0789746915860689</v>
+        <v>-0.2311596047478638</v>
       </c>
       <c r="C90" t="n">
-        <v>0.05933458394578556</v>
+        <v>-0.1592945580884303</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.07424771602539554</v>
+        <v>-0.247543485305067</v>
       </c>
       <c r="B91" t="n">
-        <v>0.03094163850767719</v>
+        <v>-0.2075745992349495</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2362791157230476</v>
+        <v>0.0951092294937413</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.06930937228988131</v>
+        <v>0.2224390700019235</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0113173297941381</v>
+        <v>0.1899812106598524</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1794291624417882</v>
+        <v>-0.04186548745281515</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.2351246877306835</v>
+        <v>0.09589180899613775</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.07439882262879213</v>
+        <v>0.1750709863286949</v>
       </c>
       <c r="C93" t="n">
-        <v>0.05675449835417941</v>
+        <v>-0.108512109613477</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.06491303884668441</v>
+        <v>-0.0642733458180679</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.0928120146829358</v>
+        <v>-0.0007230468334123697</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.03740437955289355</v>
+        <v>-0.06845361841194046</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-0.095041367705437</v>
+        <v>-0.003587131009122641</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.05172524785266465</v>
+        <v>0.2075044391863676</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2258179113374391</v>
+        <v>-0.1107485434236141</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.1243060290179261</v>
+        <v>0.08209475668993046</v>
       </c>
       <c r="B96" t="n">
-        <v>0.2169640371216868</v>
+        <v>0.09412053297786348</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.1984370892450877</v>
+        <v>0.0833448710784619</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.2309881691989668</v>
+        <v>0.103277077872958</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0622233326708402</v>
+        <v>0.2445332292169491</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.196793104880735</v>
+        <v>0.191135608272771</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.09887463670212443</v>
+        <v>0.008728970586442711</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.08490799139675073</v>
+        <v>-0.1012364618443823</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1467830532805129</v>
+        <v>-0.03001680937381879</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.2343557194574231</v>
+        <v>-2.255325772874942e-13</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.1619109179814407</v>
+        <v>-0.009003126932043359</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.09506338515744238</v>
+        <v>-1.080635747273533e-10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.2442864766400941</v>
+        <v>0.1305867659646816</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.02056882821496205</v>
+        <v>-0.02000342190976459</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1726328272652217</v>
+        <v>0.2417668752454882</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.1891904387457261</v>
+        <v>-0.1953891303711102</v>
       </c>
       <c r="B101" t="n">
-        <v>0.055063081938521</v>
+        <v>-0.07411947430542611</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0004146657569463889</v>
+        <v>-0.1437852475464936</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
@@ -441,1102 +441,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01210362052016088</v>
+        <v>0.2370027591241485</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1137027707260424</v>
+        <v>0.1272311250533292</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04431962050523962</v>
+        <v>0.1562804866171873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1999586817892291</v>
+        <v>-0.03354343143280843</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.1680874484078807</v>
+        <v>-0.2146033868421497</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07392020685380714</v>
+        <v>0.2226775579024408</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.216274209584133</v>
+        <v>-0.1708486070427294</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1449243335393811</v>
+        <v>0.08416375083081176</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02666241010495472</v>
+        <v>-0.15353713526712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.2461101646292367</v>
+        <v>-0.1788854614828783</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1206072214582163</v>
+        <v>0.1788214039189499</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1014415185692277</v>
+        <v>0.1073079524182266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1845415960062787</v>
+        <v>0.109265293481767</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.03716442132934806</v>
+        <v>0.128766998233888</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2063636095581707</v>
+        <v>-0.200135045829914</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.004820902716201437</v>
+        <v>0.06841134639146633</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.01767585065248328</v>
+        <v>0.2001679648390075</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1984348318495678</v>
+        <v>-0.04463804775727585</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.08546171060641421</v>
+        <v>-0.1371724178279158</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05064191794078829</v>
+        <v>-0.2078954872980159</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2253128665136343</v>
+        <v>-0.04528834316151841</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.1311979724010757</v>
+        <v>0.06168164157362296</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1599795779034408</v>
+        <v>0.1399762671452527</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0760439515631898</v>
+        <v>0.112959925902178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1697832141461818</v>
+        <v>9.255173375742686e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1849796649087322</v>
+        <v>-0.09853765099712766</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04487144048295318</v>
+        <v>-0.0003182509742898551</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1914108046034977</v>
+        <v>-0.1796646165311935</v>
       </c>
       <c r="B11" t="n">
-        <v>0.08386734159945955</v>
+        <v>-0.1653706396712205</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2069758950039365</v>
+        <v>-0.03533566502787238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.000338740764926229</v>
+        <v>-0.005714319891946371</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.00184957119304665</v>
+        <v>-0.03996181136703911</v>
       </c>
       <c r="C12" t="n">
-        <v>1.616123379022477e-05</v>
+        <v>-0.06140518293226558</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.03108737485621763</v>
+        <v>-0.07453171700466232</v>
       </c>
       <c r="B13" t="n">
-        <v>0.08809787101598883</v>
+        <v>-0.04470819006251676</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.02928196792609933</v>
+        <v>0.1884567237363774</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.02213007115215502</v>
+        <v>0.04126782772693252</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2149780466044623</v>
+        <v>-0.1746215523390397</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04283862793902794</v>
+        <v>0.06538791375470572</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.01041097713150759</v>
+        <v>0.0845735618228408</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.04113307066464365</v>
+        <v>0.1554457905971804</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02603502810783976</v>
+        <v>-0.04676511218880637</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2284795447213178</v>
+        <v>0.1588271545095312</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2060769764788018</v>
+        <v>-0.2435154188877283</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2363338462699098</v>
+        <v>0.04172119853420257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.05883648065591841</v>
+        <v>0.1895541816744008</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1912812101603729</v>
+        <v>0.01516908813370134</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1743828315041423</v>
+        <v>-0.01286333241512269</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1020598228169361</v>
+        <v>0.05397470567619177</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.135163061487066</v>
+        <v>-0.1539351495094606</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2229992527193982</v>
+        <v>0.1136776731222829</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1691806569359391</v>
+        <v>0.1723092317851401</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1819050255118005</v>
+        <v>0.06053512226564739</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.06662914149083801</v>
+        <v>-0.04830913325931435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1929522986084609</v>
+        <v>-0.1792241484740173</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.1324961413233522</v>
+        <v>-0.2243187652449375</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.01108445305869458</v>
+        <v>-0.1523561931950407</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.2146412948326631</v>
+        <v>-0.1641564917039225</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01029032139743344</v>
+        <v>-0.2159452404075682</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.05462453387676786</v>
+        <v>0.1561642120975529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.06402908137291642</v>
+        <v>-0.1158755342669387</v>
       </c>
       <c r="B22" t="n">
-        <v>-9.617835626890516e-09</v>
+        <v>-0.02885721739598799</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2121664415655603</v>
+        <v>0.1719941315888125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.03118660889159448</v>
+        <v>-0.1563476776284738</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.02845780906251944</v>
+        <v>-0.1324200045584916</v>
       </c>
       <c r="C23" t="n">
-        <v>-8.240560142102906e-05</v>
+        <v>0.04678326371823411</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.09799395254223628</v>
+        <v>0.2025760339894841</v>
       </c>
       <c r="B24" t="n">
-        <v>0.08410061552557388</v>
+        <v>-0.03341918082786371</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1655632402455098</v>
+        <v>0.01971218541450372</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.1754350546627619</v>
+        <v>-0.0009221808488497631</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01033857368503461</v>
+        <v>-0.0531789654522925</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.005018535103430092</v>
+        <v>-0.09463922614086971</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.1486525030540925</v>
+        <v>6.435395697471566e-06</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1340659120328411</v>
+        <v>0.04135230554348301</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01814946479467297</v>
+        <v>-0.002895964470439016</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.123175538477813</v>
+        <v>-0.03970770680116582</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1040434795361554</v>
+        <v>0.1825168585108398</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1289687993226445</v>
+        <v>0.16003945168401</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.2333591323909409</v>
+        <v>0.09661214572675041</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.1359870752657822</v>
+        <v>-0.01931423274365661</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1706614395331824</v>
+        <v>0.006236960903085068</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.09466474842899737</v>
+        <v>-0.05223817614024858</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.1470731718993727</v>
+        <v>-0.009428731880941033</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09675081967273866</v>
+        <v>-0.04594412588625396</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.03170187298491894</v>
+        <v>-0.0006188772903811788</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.2246499371026885</v>
+        <v>-0.02102823387611271</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2065658858865287</v>
+        <v>2.741212140666256e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.1666925976186634</v>
+        <v>-0.006101849575206318</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.04707225553828176</v>
+        <v>0.1965156383792069</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1179899482496636</v>
+        <v>-0.08024124321951176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.09856269879864725</v>
+        <v>0.05818026761709656</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1709930166147157</v>
+        <v>-0.0001859215442351589</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09099499289440634</v>
+        <v>0.0003997106494013655</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.01716643915916196</v>
+        <v>-0.1492730556754602</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.1469700746482046</v>
+        <v>-0.1764304535730364</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1786035814518295</v>
+        <v>0.042412755132411</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.05169602606667583</v>
+        <v>0.2502423367668412</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1208591653029723</v>
+        <v>-0.1548417957037816</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1109202490538979</v>
+        <v>0.09159083712587604</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.04227027272148021</v>
+        <v>-0.06491085899152799</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.1740056855807975</v>
+        <v>-0.03773716128616764</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1462717563071722</v>
+        <v>0.1088828623554937</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.2314045316407442</v>
+        <v>0.06313752677687046</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.1505372735345572</v>
+        <v>0.05017713349936104</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2250700647577389</v>
+        <v>-0.1227274345050783</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.02168531968721452</v>
+        <v>3.187606991279516e-07</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1023834965588014</v>
+        <v>-0.02060582516212685</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.100227285822991</v>
+        <v>-0.06251192356817233</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.06153236798329952</v>
+        <v>-0.2096228879396544</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.2208413330737243</v>
+        <v>-0.1441732809800158</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2280601448740299</v>
+        <v>-0.2030187205645617</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.2132747728486415</v>
+        <v>-0.08197540209731269</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2129255421798786</v>
+        <v>-0.2360809348887173</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2328562500830196</v>
+        <v>-0.1754382558522735</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.1234061178880579</v>
+        <v>0.04861733051017215</v>
       </c>
       <c r="B40" t="n">
-        <v>0.06552015940222125</v>
+        <v>0.02553623331751785</v>
       </c>
       <c r="C40" t="n">
-        <v>0.137169766751453</v>
+        <v>-0.06512026949933228</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.2046289038863549</v>
+        <v>0.07355661968849039</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.2110806202892935</v>
+        <v>0.03051373455343871</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.06853454396163873</v>
+        <v>-0.161834215076364</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.1772067292850775</v>
+        <v>0.1098935989275933</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.1195752227907606</v>
+        <v>-1.817688367327341e-06</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.143295155689667</v>
+        <v>0.1014583111971537</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.07682625980587904</v>
+        <v>0.06551738603402203</v>
       </c>
       <c r="B43" t="n">
-        <v>0.006545432286438919</v>
+        <v>-0.2364338147851568</v>
       </c>
       <c r="C43" t="n">
-        <v>0.04280840310651261</v>
+        <v>0.1928788569280975</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.1615625357720086</v>
+        <v>0.1843578906930468</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.1203654218029473</v>
+        <v>0.2055122077890167</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.01484098613409475</v>
+        <v>0.1484160315019779</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.1812256191852517</v>
+        <v>0.1219294997357742</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.03027204388961807</v>
+        <v>-0.07739427884347991</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.05782238279706713</v>
+        <v>-0.1197814866321747</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.1123354649118858</v>
+        <v>-0.07033469919179292</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.1401149507341461</v>
+        <v>-0.01739149171194604</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.05539843608296291</v>
+        <v>-1.171633618553079e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5.141442444903261e-11</v>
+        <v>-0.06383166330405135</v>
       </c>
       <c r="B47" t="n">
-        <v>5.237685760033048e-10</v>
+        <v>-0.008141804434631783</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0006829735291770644</v>
+        <v>0.0008056046503959002</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.001202000787823855</v>
+        <v>0.1887896854598726</v>
       </c>
       <c r="B48" t="n">
-        <v>0.001978699185609517</v>
+        <v>0.09166249122219655</v>
       </c>
       <c r="C48" t="n">
-        <v>0.001167433080304127</v>
+        <v>-0.1894280460266218</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.1130988944704425</v>
+        <v>-1.267744768574589e-05</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1626980322383159</v>
+        <v>0.03643469592445154</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01030629015914353</v>
+        <v>0.04374044438337219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.1715901962451064</v>
+        <v>-0.05006699256596159</v>
       </c>
       <c r="B50" t="n">
-        <v>0.04611585041462059</v>
+        <v>-0.1054178142462956</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1372587917139371</v>
+        <v>-4.805994834634405e-06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.1964583220901348</v>
+        <v>-0.1371967004912117</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.1679837971361418</v>
+        <v>-0.2250533885554661</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.02250437605027689</v>
+        <v>0.1953353066657634</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.1479201493849999</v>
+        <v>-0.2238716958283256</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.03104841588993119</v>
+        <v>-0.084749435617872</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.07030894304916972</v>
+        <v>0.007647739970300826</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.2168494681952689</v>
+        <v>-0.008260136637810259</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.1382728908265186</v>
+        <v>-0.01913296326476134</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2221166518897794</v>
+        <v>-0.08188570666288064</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.1168818084350754</v>
+        <v>0.009789215368107177</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1542846748760279</v>
+        <v>0.1283797041659084</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1256576725063225</v>
+        <v>0.1996026952476533</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.07354511695087128</v>
+        <v>-0.0202215691584814</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1671610952881677</v>
+        <v>-0.009177381798494432</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1456125947139978</v>
+        <v>0.01215480808988676</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.1335289956808442</v>
+        <v>-0.1048278388603433</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2276685738070083</v>
+        <v>-0.0351090957819759</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.04056744059968691</v>
+        <v>0.01894764587325997</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.01983890554358759</v>
+        <v>-0.01956444393319015</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.2044939135950287</v>
+        <v>0.1518979973889226</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1747939948527393</v>
+        <v>-0.146575086089812</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.06199898973498199</v>
+        <v>0.225623719903612</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1665649372224167</v>
+        <v>0.122345273587313</v>
       </c>
       <c r="C58" t="n">
-        <v>0.04057354755482517</v>
+        <v>0.03360323520742503</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1631920648567337</v>
+        <v>0.1038235532123856</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.1138971955549825</v>
+        <v>-0.02949396745967699</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1278680228826398</v>
+        <v>0.09969900579880465</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.09093040783992744</v>
+        <v>-0.02666350886246515</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.1431356930028631</v>
+        <v>-0.1065824179196314</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1413816522145883</v>
+        <v>0.1273450291291061</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.0001916000322994933</v>
+        <v>0.2067087015839505</v>
       </c>
       <c r="B61" t="n">
-        <v>0.01054401077734958</v>
+        <v>0.02442198170609497</v>
       </c>
       <c r="C61" t="n">
-        <v>1.153513763205981e-07</v>
+        <v>0.09370271075452737</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.101912970012308</v>
+        <v>-0.156173796766552</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1719446125746868</v>
+        <v>0.09852207843363232</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1994796716138168</v>
+        <v>-0.07000552216675714</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1140954834448455</v>
+        <v>-0.1063270003605283</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.05222123885022036</v>
+        <v>0.0005829778127692702</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.08596579259932825</v>
+        <v>0.0001228650320040259</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.0001837166994705889</v>
+        <v>-0.2217826391317018</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.02259890932793061</v>
+        <v>0.237124969061533</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.04931176392208086</v>
+        <v>0.2160994154162156</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.1155324207199708</v>
+        <v>0.01819118849677278</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.2210733697617061</v>
+        <v>-0.03965695844263648</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2389200220527465</v>
+        <v>-0.01073936548906877</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.1162765011008443</v>
+        <v>-0.004448011587177578</v>
       </c>
       <c r="B66" t="n">
-        <v>0.05455831061465435</v>
+        <v>0.1220085279659894</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.04831438357741807</v>
+        <v>0.05929564041597388</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.02153841549610707</v>
+        <v>0.2299967026277693</v>
       </c>
       <c r="B67" t="n">
-        <v>0.08795533753134892</v>
+        <v>0.1817946514695809</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1485925837878347</v>
+        <v>-0.1932830175934041</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.225341082227543</v>
+        <v>-0.06246659738994013</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.02485002308670174</v>
+        <v>0.02066296496304579</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.002060242555181945</v>
+        <v>-0.0296873599674183</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.1465120941399749</v>
+        <v>0.168594392185345</v>
       </c>
       <c r="B69" t="n">
-        <v>0.06579762640077647</v>
+        <v>0.1559271544931347</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2320046470036324</v>
+        <v>-0.04371107768290582</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.142971555039699</v>
+        <v>-0.2219975508802132</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.07386487005547433</v>
+        <v>-0.06607176082820393</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1407396158625648</v>
+        <v>-0.2092529382316074</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.01211910382949168</v>
+        <v>0.2173131876219246</v>
       </c>
       <c r="B71" t="n">
-        <v>0.144457125867218</v>
+        <v>-0.2393852491647848</v>
       </c>
       <c r="C71" t="n">
-        <v>0.06220040081469529</v>
+        <v>0.05522721172914109</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>8.951193774234825e-07</v>
+        <v>-0.04375014952011379</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.0314484185481593</v>
+        <v>-0.01857096498877823</v>
       </c>
       <c r="C72" t="n">
-        <v>1.727502572750668e-05</v>
+        <v>-0.02745753744865998</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-5.313352468007647e-10</v>
+        <v>0.009680186294351698</v>
       </c>
       <c r="B73" t="n">
-        <v>0.01986044868470015</v>
+        <v>0.003122628693714899</v>
       </c>
       <c r="C73" t="n">
-        <v>8.513342831843539e-05</v>
+        <v>0.07602141550479793</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.04288665411421533</v>
+        <v>-0.08408105155893542</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.09564388879223766</v>
+        <v>0.0595030559885405</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2092881621080661</v>
+        <v>-0.1659914488417256</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-1.122043559573601e-08</v>
+        <v>0.06631632708330895</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0008101374567341666</v>
+        <v>0.2133622465923129</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.01842463109439616</v>
+        <v>-0.05555913717756283</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.150548741837869</v>
+        <v>0.2192642065315563</v>
       </c>
       <c r="B76" t="n">
-        <v>0.07955158755047434</v>
+        <v>0.1432291527742358</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2222822316750688</v>
+        <v>0.06350523879034925</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6.07827306130887e-06</v>
+        <v>0.1511476299192165</v>
       </c>
       <c r="B77" t="n">
-        <v>0.003877149729844037</v>
+        <v>-0.2515724280187516</v>
       </c>
       <c r="C77" t="n">
-        <v>0.001600234095611573</v>
+        <v>-0.1789751460453545</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.07775929850822171</v>
+        <v>-0.1357196329080567</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1425104752694273</v>
+        <v>0.1790987071659405</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04141778599548119</v>
+        <v>-0.07401944841582445</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.1707879625765426</v>
+        <v>0.07992566678980002</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.1284983795817152</v>
+        <v>0.1075576013857719</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2059719953310357</v>
+        <v>-0.1693447918887088</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.001605108234900618</v>
+        <v>-0.03292563241702461</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.01790301598523839</v>
+        <v>0.02936990063482901</v>
       </c>
       <c r="C80" t="n">
-        <v>0.001844699051390847</v>
+        <v>-0.02412400545985043</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.0005498147212081143</v>
+        <v>0.1277475703068097</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.001234030286833605</v>
+        <v>0.1886865692019046</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.00286526477589508</v>
+        <v>-0.1767300783939888</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.2434355753070539</v>
+        <v>0.02273008586409173</v>
       </c>
       <c r="B82" t="n">
-        <v>0.000534515010480052</v>
+        <v>0.08218501030482228</v>
       </c>
       <c r="C82" t="n">
-        <v>0.01862058388525854</v>
+        <v>-0.01820502597400412</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.2001218782566054</v>
+        <v>-0.2525380728572527</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1712620472621791</v>
+        <v>0.2361253302787947</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1367105003000828</v>
+        <v>0.2342194160099597</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-0.1160139248092407</v>
+        <v>0.1433000163966183</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.1382412184791703</v>
+        <v>-0.1537935548742381</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1248792616613697</v>
+        <v>-0.1614817513096002</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.2091220682353377</v>
+        <v>0.0780631337265638</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.02660210402539178</v>
+        <v>0.09452057242945495</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.08525320645153285</v>
+        <v>0.1105065253832823</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>8.801965675219919e-05</v>
+        <v>0.2285499583932876</v>
       </c>
       <c r="B86" t="n">
-        <v>-3.878540357103219e-05</v>
+        <v>-0.02898692059671786</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.007668642462300281</v>
+        <v>-0.2489746870134141</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.1121027669334636</v>
+        <v>-0.0423631803872563</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2289859706833824</v>
+        <v>-0.2169058907176299</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.1318314112616442</v>
+        <v>-0.2000344514889962</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.1584775369851397</v>
+        <v>-0.2168390810229781</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.155914349858095</v>
+        <v>0.09444647388340267</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1683665080388387</v>
+        <v>-0.06599657477212779</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.01333229320358377</v>
+        <v>0.200394222020766</v>
       </c>
       <c r="B89" t="n">
-        <v>-4.680805752566217e-05</v>
+        <v>-0.06249225895684241</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.01571014054063195</v>
+        <v>-0.2153116219652961</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.227467040028459</v>
+        <v>-0.03752523661290539</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.2311596047478638</v>
+        <v>-0.2414439158655328</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.1592945580884303</v>
+        <v>-0.04692828794246685</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.247543485305067</v>
+        <v>-0.1805616144855941</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.2075745992349495</v>
+        <v>0.2277838581121944</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0951092294937413</v>
+        <v>-0.1261376207153204</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.2224390700019235</v>
+        <v>-0.07042392018488131</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1899812106598524</v>
+        <v>0.2220857179055844</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.04186548745281515</v>
+        <v>-0.1053437728047809</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.09589180899613775</v>
+        <v>-0.03159484869108555</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1750709863286949</v>
+        <v>0.07611732200128407</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.108512109613477</v>
+        <v>-0.1997568851994988</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.0642733458180679</v>
+        <v>0.0743497147668767</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.0007230468334123697</v>
+        <v>-0.06206112186036367</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.06845361841194046</v>
+        <v>-0.04699873783147841</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-0.003587131009122641</v>
+        <v>0.2899041920882398</v>
       </c>
       <c r="B95" t="n">
-        <v>0.2075044391863676</v>
+        <v>0.102662196982266</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1107485434236141</v>
+        <v>-0.07282779730427347</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.08209475668993046</v>
+        <v>0.0005563881512086128</v>
       </c>
       <c r="B96" t="n">
-        <v>0.09412053297786348</v>
+        <v>0.03843278898493687</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0833448710784619</v>
+        <v>0.00151363099251353</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.103277077872958</v>
+        <v>0.03309443450074047</v>
       </c>
       <c r="B97" t="n">
-        <v>0.2445332292169491</v>
+        <v>0.1533925887707281</v>
       </c>
       <c r="C97" t="n">
-        <v>0.191135608272771</v>
+        <v>0.01672698473069629</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.008728970586442711</v>
+        <v>-0.0842402057267337</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.1012364618443823</v>
+        <v>0.03832406741525578</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.03001680937381879</v>
+        <v>-0.1104735306171279</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-2.255325772874942e-13</v>
+        <v>0.002103434500355402</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.009003126932043359</v>
+        <v>0.1708928287486249</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.080635747273533e-10</v>
+        <v>0.2124058652593457</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.1305867659646816</v>
+        <v>-0.004648584058053563</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.02000342190976459</v>
+        <v>0.004448443760916747</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2417668752454882</v>
+        <v>0.05443950787786893</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.1953891303711102</v>
+        <v>0.01218156125603097</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.07411947430542611</v>
+        <v>0.1000899486476355</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.1437852475464936</v>
+        <v>-0.01762475609603689</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
@@ -441,1102 +441,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.2370027591241485</v>
+        <v>0.08646970202817632</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1272311250533292</v>
+        <v>-0.1140036244008244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1562804866171873</v>
+        <v>0.06890462061233918</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03354343143280843</v>
+        <v>0.1173538153291193</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2146033868421497</v>
+        <v>0.07176483680436435</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2226775579024408</v>
+        <v>-0.162986924136291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.1708486070427294</v>
+        <v>-0.02076162569179982</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08416375083081176</v>
+        <v>0.226041929149473</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.15353713526712</v>
+        <v>-0.03660598908666729</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.1788854614828783</v>
+        <v>0.01595736392768053</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1788214039189499</v>
+        <v>-0.02927657103297716</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1073079524182266</v>
+        <v>0.2314315896994811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.109265293481767</v>
+        <v>-0.2229229998962399</v>
       </c>
       <c r="B6" t="n">
-        <v>0.128766998233888</v>
+        <v>0.0921055485792824</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.200135045829914</v>
+        <v>0.01593232503362858</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.06841134639146633</v>
+        <v>0.1053752402979152</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2001679648390075</v>
+        <v>-0.006025272029283137</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.04463804775727585</v>
+        <v>-0.1162256647131659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.1371724178279158</v>
+        <v>0.0457020051154587</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2078954872980159</v>
+        <v>0.008092442451685508</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.04528834316151841</v>
+        <v>0.1066131859684052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.06168164157362296</v>
+        <v>-0.1216231839998391</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1399762671452527</v>
+        <v>-0.05889363533053949</v>
       </c>
       <c r="C9" t="n">
-        <v>0.112959925902178</v>
+        <v>0.0011004751380661</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9.255173375742686e-05</v>
+        <v>-0.1700957559145136</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.09853765099712766</v>
+        <v>-0.1902760771270562</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0003182509742898551</v>
+        <v>-0.1979080764301991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1796646165311935</v>
+        <v>-0.02019015472539007</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.1653706396712205</v>
+        <v>-0.1051313070594899</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.03533566502787238</v>
+        <v>-0.2255623566867206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.005714319891946371</v>
+        <v>0.0723829739109131</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.03996181136703911</v>
+        <v>0.196461986961059</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.06140518293226558</v>
+        <v>-0.1144500456811398</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.07453171700466232</v>
+        <v>0.2405844033572513</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.04470819006251676</v>
+        <v>0.1081341745460567</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1884567237363774</v>
+        <v>-0.1544804427359155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.04126782772693252</v>
+        <v>-0.1087721297148089</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.1746215523390397</v>
+        <v>-0.2528929548619363</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06538791375470572</v>
+        <v>-0.1087064844012539</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0845735618228408</v>
+        <v>-0.001011193250341505</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1554457905971804</v>
+        <v>-0.004389656639624622</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.04676511218880637</v>
+        <v>-0.01064679631486314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1588271545095312</v>
+        <v>-0.1278503874264703</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.2435154188877283</v>
+        <v>-0.05474033853186335</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04172119853420257</v>
+        <v>0.01869900385454432</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1895541816744008</v>
+        <v>0.2250531389105157</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01516908813370134</v>
+        <v>-0.06568267820501411</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.01286333241512269</v>
+        <v>0.1229003324508724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.05397470567619177</v>
+        <v>0.0107248447666807</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.1539351495094606</v>
+        <v>-8.216804616361181e-06</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1136776731222829</v>
+        <v>0.06735891053444723</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1723092317851401</v>
+        <v>0.203024637635016</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06053512226564739</v>
+        <v>0.1433388607458987</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.04830913325931435</v>
+        <v>0.133959459286084</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1792241484740173</v>
+        <v>-0.129953879553522</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.2243187652449375</v>
+        <v>0.2096243683693007</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1523561931950407</v>
+        <v>-0.02614184438853027</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.1641564917039225</v>
+        <v>-0.02889500406252479</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.2159452404075682</v>
+        <v>0.1238898536706083</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1561642120975529</v>
+        <v>-0.1570929380792256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.1158755342669387</v>
+        <v>0.1217697083726979</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.02885721739598799</v>
+        <v>0.1774395040596514</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1719941315888125</v>
+        <v>0.2399928370962979</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.1563476776284738</v>
+        <v>-0.1035612506478312</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.1324200045584916</v>
+        <v>0.02838519750330683</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04678326371823411</v>
+        <v>-0.00499020859236424</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.2025760339894841</v>
+        <v>0.1329847880027532</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.03341918082786371</v>
+        <v>-0.1485417355742632</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01971218541450372</v>
+        <v>0.1455455546971928</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.0009221808488497631</v>
+        <v>0.1912602684642669</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0531789654522925</v>
+        <v>0.1556515994059374</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.09463922614086971</v>
+        <v>0.1117322969819125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6.435395697471566e-06</v>
+        <v>-0.02885660124503111</v>
       </c>
       <c r="B26" t="n">
-        <v>0.04135230554348301</v>
+        <v>-0.2186574203218374</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.002895964470439016</v>
+        <v>0.233757898951333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.03970770680116582</v>
+        <v>0.01097818203993587</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1825168585108398</v>
+        <v>0.04179569194321435</v>
       </c>
       <c r="C27" t="n">
-        <v>0.16003945168401</v>
+        <v>0.1340802072032345</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.09661214572675041</v>
+        <v>0.01672519685002759</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.01931423274365661</v>
+        <v>0.08120964443376873</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006236960903085068</v>
+        <v>-0.07988014362458565</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.05223817614024858</v>
+        <v>0.04323312104259219</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.009428731880941033</v>
+        <v>-0.1334237099084442</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.04594412588625396</v>
+        <v>-0.1897510122090456</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.0006188772903811788</v>
+        <v>-0.08554490576103013</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.02102823387611271</v>
+        <v>-0.05551895066147838</v>
       </c>
       <c r="C30" t="n">
-        <v>2.741212140666256e-05</v>
+        <v>-0.1982771881105537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.006101849575206318</v>
+        <v>0.06182795358388116</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1965156383792069</v>
+        <v>-0.03520799100435661</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.08024124321951176</v>
+        <v>-0.03643778470097583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.05818026761709656</v>
+        <v>-0.2297281588866565</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.0001859215442351589</v>
+        <v>0.1588388635057827</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0003997106494013655</v>
+        <v>-0.2215768806396208</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.1492730556754602</v>
+        <v>0.2562660833153811</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.1764304535730364</v>
+        <v>0.0045493004488093</v>
       </c>
       <c r="C33" t="n">
-        <v>0.042412755132411</v>
+        <v>-0.2254969417702486</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2502423367668412</v>
+        <v>0.142304455057161</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.1548417957037816</v>
+        <v>-0.07230737535050842</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09159083712587604</v>
+        <v>-0.09356256657242167</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.06491085899152799</v>
+        <v>-0.04339059945496206</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.03773716128616764</v>
+        <v>0.0009684950753398205</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1088828623554937</v>
+        <v>0.02328000029441792</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.06313752677687046</v>
+        <v>-0.1005805228991082</v>
       </c>
       <c r="B36" t="n">
-        <v>0.05017713349936104</v>
+        <v>-0.1468893181206581</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1227274345050783</v>
+        <v>-0.1699317805083427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3.187606991279516e-07</v>
+        <v>0.01880247865139576</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.02060582516212685</v>
+        <v>0.09235175384438585</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.06251192356817233</v>
+        <v>-0.09857599270966265</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.2096228879396544</v>
+        <v>-0.1239754796518424</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.1441732809800158</v>
+        <v>-0.04457721295106053</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2030187205645617</v>
+        <v>0.0002960435473253412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.08197540209731269</v>
+        <v>-0.1886675675235801</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.2360809348887173</v>
+        <v>0.1041772940791862</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1754382558522735</v>
+        <v>-0.127734451783682</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.04861733051017215</v>
+        <v>0.05772823813044495</v>
       </c>
       <c r="B40" t="n">
-        <v>0.02553623331751785</v>
+        <v>0.02988229391979072</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.06512026949933228</v>
+        <v>-0.1384567082707876</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.07355661968849039</v>
+        <v>-0.2084192045829618</v>
       </c>
       <c r="B41" t="n">
-        <v>0.03051373455343871</v>
+        <v>-0.1336432990745182</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.161834215076364</v>
+        <v>-0.0246653674656894</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.1098935989275933</v>
+        <v>-0.02020480550302881</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.817688367327341e-06</v>
+        <v>0.07735137256004904</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1014583111971537</v>
+        <v>-0.09100078314940994</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.06551738603402203</v>
+        <v>0.09113002850320487</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.2364338147851568</v>
+        <v>0.07148712315013216</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1928788569280975</v>
+        <v>-0.06292321672851209</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.1843578906930468</v>
+        <v>-0.02571857271666509</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2055122077890167</v>
+        <v>0.04503879096083943</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1484160315019779</v>
+        <v>-0.1466340670506451</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.1219294997357742</v>
+        <v>0.05104790690956946</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.07739427884347991</v>
+        <v>-0.00918235959045955</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1197814866321747</v>
+        <v>0.05059832669159912</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.07033469919179292</v>
+        <v>-0.08011067483241256</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.01739149171194604</v>
+        <v>-0.04642534948033446</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.171633618553079e-05</v>
+        <v>0.09232594304557495</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.06383166330405135</v>
+        <v>-0.1067471217500679</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.008141804434631783</v>
+        <v>-0.09511773280793479</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0008056046503959002</v>
+        <v>-0.1159744662108056</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.1887896854598726</v>
+        <v>0.0394700891374693</v>
       </c>
       <c r="B48" t="n">
-        <v>0.09166249122219655</v>
+        <v>0.1320666060637212</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1894280460266218</v>
+        <v>0.1364115943562265</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.267744768574589e-05</v>
+        <v>-0.2297220366950262</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03643469592445154</v>
+        <v>-0.0281487475557416</v>
       </c>
       <c r="C49" t="n">
-        <v>0.04374044438337219</v>
+        <v>-0.1340689961936511</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.05006699256596159</v>
+        <v>-0.01647333406046875</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.1054178142462956</v>
+        <v>-0.0001955141893396664</v>
       </c>
       <c r="C50" t="n">
-        <v>-4.805994834634405e-06</v>
+        <v>2.190299691958381e-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.1371967004912117</v>
+        <v>0.2189429139672559</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.2250533885554661</v>
+        <v>0.03115624484235803</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1953353066657634</v>
+        <v>-0.05932545978611051</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.2238716958283256</v>
+        <v>0.07987322674868037</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.084749435617872</v>
+        <v>0.1975146325752735</v>
       </c>
       <c r="C52" t="n">
-        <v>0.007647739970300826</v>
+        <v>0.1926229068517954</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.008260136637810259</v>
+        <v>0.01886147818447666</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.01913296326476134</v>
+        <v>0.1727676056433121</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.08188570666288064</v>
+        <v>-0.02330531935086945</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.009789215368107177</v>
+        <v>0.2488108114787251</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1283797041659084</v>
+        <v>0.00200816646766832</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1996026952476533</v>
+        <v>-0.2151040599557803</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.0202215691584814</v>
+        <v>-0.03998982626271385</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.009177381798494432</v>
+        <v>-0.2195565755097584</v>
       </c>
       <c r="C55" t="n">
-        <v>0.01215480808988676</v>
+        <v>0.03453013488473385</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.1048278388603433</v>
+        <v>0.2019204145619183</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.0351090957819759</v>
+        <v>-0.164007862186545</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01894764587325997</v>
+        <v>0.09883957680822511</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.01956444393319015</v>
+        <v>-0.1172796646784442</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1518979973889226</v>
+        <v>0.0359382327313208</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.146575086089812</v>
+        <v>0.07544597997366245</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.225623719903612</v>
+        <v>0.1908750681116815</v>
       </c>
       <c r="B58" t="n">
-        <v>0.122345273587313</v>
+        <v>0.198042434351316</v>
       </c>
       <c r="C58" t="n">
-        <v>0.03360323520742503</v>
+        <v>0.1466046910215337</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1038235532123856</v>
+        <v>0.1547820923380488</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.02949396745967699</v>
+        <v>0.1058439070900025</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09969900579880465</v>
+        <v>-0.1192713889191288</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.02666350886246515</v>
+        <v>0.05123943232035304</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.1065824179196314</v>
+        <v>0.08367136581023848</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1273450291291061</v>
+        <v>0.1762543670549381</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.2067087015839505</v>
+        <v>0.1192275857694841</v>
       </c>
       <c r="B61" t="n">
-        <v>0.02442198170609497</v>
+        <v>0.1973411321456436</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09370271075452737</v>
+        <v>0.1353945205940151</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.156173796766552</v>
+        <v>-0.1699930679446892</v>
       </c>
       <c r="B62" t="n">
-        <v>0.09852207843363232</v>
+        <v>-0.0620288529364102</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.07000552216675714</v>
+        <v>-0.04006193932764761</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.1063270003605283</v>
+        <v>-0.01627785573845848</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0005829778127692702</v>
+        <v>0.1289764658739906</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0001228650320040259</v>
+        <v>0.1717907883545496</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.2217826391317018</v>
+        <v>0.07001261666705887</v>
       </c>
       <c r="B64" t="n">
-        <v>0.237124969061533</v>
+        <v>-0.08045452098188738</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2160994154162156</v>
+        <v>0.2021529045912341</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.01819118849677278</v>
+        <v>-0.1049216843822858</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.03965695844263648</v>
+        <v>0.1485896192124071</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.01073936548906877</v>
+        <v>0.2205833293676338</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.004448011587177578</v>
+        <v>0.2433277520443399</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1220085279659894</v>
+        <v>-0.07384114310725094</v>
       </c>
       <c r="C66" t="n">
-        <v>0.05929564041597388</v>
+        <v>-0.09424063364035468</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.2299967026277693</v>
+        <v>0.195156800834296</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1817946514695809</v>
+        <v>-0.1562267903481281</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1932830175934041</v>
+        <v>-0.1097068188743901</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.06246659738994013</v>
+        <v>0.121174766777664</v>
       </c>
       <c r="B68" t="n">
-        <v>0.02066296496304579</v>
+        <v>0.1507290853373384</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0296873599674183</v>
+        <v>0.2135946959257987</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.168594392185345</v>
+        <v>-0.08334302118617631</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1559271544931347</v>
+        <v>-0.2581251179644778</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.04371107768290582</v>
+        <v>0.151958829213733</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.2219975508802132</v>
+        <v>-0.004477960810100426</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.06607176082820393</v>
+        <v>-2.197320111889579e-05</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2092529382316074</v>
+        <v>-0.02005496074224102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.2173131876219246</v>
+        <v>0.01576233622807991</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.2393852491647848</v>
+        <v>0.06677770723068467</v>
       </c>
       <c r="C71" t="n">
-        <v>0.05522721172914109</v>
+        <v>0.1388864702672244</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.04375014952011379</v>
+        <v>0.1129289648883715</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.01857096498877823</v>
+        <v>0.16464188383924</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.02745753744865998</v>
+        <v>-0.05901200565010573</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.009680186294351698</v>
+        <v>0.2348094704859902</v>
       </c>
       <c r="B73" t="n">
-        <v>0.003122628693714899</v>
+        <v>-0.1114723670297355</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07602141550479793</v>
+        <v>-0.01835019283818747</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.08408105155893542</v>
+        <v>-0.1970926472802825</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0595030559885405</v>
+        <v>-0.1072566420325369</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1659914488417256</v>
+        <v>-0.1583690074781754</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.06631632708330895</v>
+        <v>0.118157415233733</v>
       </c>
       <c r="B75" t="n">
-        <v>0.2133622465923129</v>
+        <v>0.05139574683980898</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.05555913717756283</v>
+        <v>0.02922714563046574</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.2192642065315563</v>
+        <v>0.023100869775905</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1432291527742358</v>
+        <v>0.1386898635161345</v>
       </c>
       <c r="C76" t="n">
-        <v>0.06350523879034925</v>
+        <v>0.087277024649594</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.1511476299192165</v>
+        <v>-0.04401983904827874</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.2515724280187516</v>
+        <v>0.086687772736405</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1789751460453545</v>
+        <v>0.02138188647231769</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.1357196329080567</v>
+        <v>-0.08644429181232634</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1790987071659405</v>
+        <v>0.001425206084164916</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.07401944841582445</v>
+        <v>0.09507875753242066</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.07992566678980002</v>
+        <v>-0.2091720149319188</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1075576013857719</v>
+        <v>0.0911532220349018</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1693447918887088</v>
+        <v>-0.2160040236918948</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.03292563241702461</v>
+        <v>0.04764469311546721</v>
       </c>
       <c r="B80" t="n">
-        <v>0.02936990063482901</v>
+        <v>0.2019430219474124</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.02412400545985043</v>
+        <v>-0.03926236730055557</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.1277475703068097</v>
+        <v>-0.09750990019134227</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1886865692019046</v>
+        <v>0.08088276177368395</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1767300783939888</v>
+        <v>-0.06210493876394452</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.02273008586409173</v>
+        <v>-0.2343968891506727</v>
       </c>
       <c r="B82" t="n">
-        <v>0.08218501030482228</v>
+        <v>0.1634077345675888</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.01820502597400412</v>
+        <v>0.06677958083256491</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-0.2525380728572527</v>
+        <v>0.1093498775223214</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2361253302787947</v>
+        <v>0.006347834953112774</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2342194160099597</v>
+        <v>0.1999465247490166</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.1433000163966183</v>
+        <v>0.06644998924307427</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.1537935548742381</v>
+        <v>0.005932816888212494</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.1614817513096002</v>
+        <v>0.03675993284921616</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.0780631337265638</v>
+        <v>0.110178124964978</v>
       </c>
       <c r="B85" t="n">
-        <v>0.09452057242945495</v>
+        <v>-0.06996123737942163</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1105065253832823</v>
+        <v>-0.2214206171122779</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.2285499583932876</v>
+        <v>0.1754845142392009</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.02898692059671786</v>
+        <v>-0.1231497565182557</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.2489746870134141</v>
+        <v>0.1839656225704099</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.0423631803872563</v>
+        <v>6.719242340761736e-06</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.2169058907176299</v>
+        <v>-0.0103586647953789</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.2000344514889962</v>
+        <v>-0.0425414566037965</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.2168390810229781</v>
+        <v>-0.0171605356661551</v>
       </c>
       <c r="B88" t="n">
-        <v>0.09444647388340267</v>
+        <v>-0.01970312242098261</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.06599657477212779</v>
+        <v>0.04824196168914659</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.200394222020766</v>
+        <v>-0.08427212051307895</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.06249225895684241</v>
+        <v>-0.09509131116459488</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.2153116219652961</v>
+        <v>-0.05206058560216675</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.03752523661290539</v>
+        <v>0.05709718909638181</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.2414439158655328</v>
+        <v>-0.09803445673588952</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.04692828794246685</v>
+        <v>0.2289133322711678</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.1805616144855941</v>
+        <v>0.03322259904820656</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2277838581121944</v>
+        <v>-0.08139316641455654</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.1261376207153204</v>
+        <v>0.008371812508733808</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.07042392018488131</v>
+        <v>0.07026920724744055</v>
       </c>
       <c r="B92" t="n">
-        <v>0.2220857179055844</v>
+        <v>0.169904207058517</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.1053437728047809</v>
+        <v>-0.1230567584975749</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.03159484869108555</v>
+        <v>-0.001662657639571471</v>
       </c>
       <c r="B93" t="n">
-        <v>0.07611732200128407</v>
+        <v>-0.05203858419365098</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1997568851994988</v>
+        <v>0.02116291832671592</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.0743497147668767</v>
+        <v>0.1029049615245028</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.06206112186036367</v>
+        <v>-0.1816140553461547</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.04699873783147841</v>
+        <v>-0.03770220620845842</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.2899041920882398</v>
+        <v>0.1065050824703524</v>
       </c>
       <c r="B95" t="n">
-        <v>0.102662196982266</v>
+        <v>-0.003446518637643252</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.07282779730427347</v>
+        <v>0.03146023032126417</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.0005563881512086128</v>
+        <v>0.001362700770733395</v>
       </c>
       <c r="B96" t="n">
-        <v>0.03843278898493687</v>
+        <v>-0.002145219606877759</v>
       </c>
       <c r="C96" t="n">
-        <v>0.00151363099251353</v>
+        <v>-0.02810835869300101</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.03309443450074047</v>
+        <v>-0.1546481156479921</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1533925887707281</v>
+        <v>0.05382472326628216</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01672698473069629</v>
+        <v>-0.06672087140914339</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-0.0842402057267337</v>
+        <v>0.1981537867959856</v>
       </c>
       <c r="B98" t="n">
-        <v>0.03832406741525578</v>
+        <v>-0.1816369504616887</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1104735306171279</v>
+        <v>-0.1315972536813401</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.002103434500355402</v>
+        <v>0.1552566907962881</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1708928287486249</v>
+        <v>0.07632399674775397</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2124058652593457</v>
+        <v>-0.1876800628269002</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.004648584058053563</v>
+        <v>0.2075730890929521</v>
       </c>
       <c r="B100" t="n">
-        <v>0.004448443760916747</v>
+        <v>-0.1887571300020568</v>
       </c>
       <c r="C100" t="n">
-        <v>0.05443950787786893</v>
+        <v>0.1544405175148515</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.01218156125603097</v>
+        <v>-0.02933777715262977</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1000899486476355</v>
+        <v>0.1626512485349868</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.01762475609603689</v>
+        <v>0.07198794821201651</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
@@ -441,1102 +441,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.08646970202817632</v>
+        <v>-0.02811170763267307</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1140036244008244</v>
+        <v>-0.07826125238725755</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06890462061233918</v>
+        <v>0.05198639412035283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1173538153291193</v>
+        <v>-2.351635644831681e-08</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07176483680436435</v>
+        <v>-5.580417678848953e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.162986924136291</v>
+        <v>0.04645806377777716</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.02076162569179982</v>
+        <v>-0.09835942099761995</v>
       </c>
       <c r="B4" t="n">
-        <v>0.226041929149473</v>
+        <v>-0.1756713247155781</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.03660598908666729</v>
+        <v>-0.0604118366227008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.01595736392768053</v>
+        <v>-0.1162188321043618</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.02927657103297716</v>
+        <v>-0.1669275378842655</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2314315896994811</v>
+        <v>-0.1464219374597453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.2229229998962399</v>
+        <v>-0.007985147590942421</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0921055485792824</v>
+        <v>-0.02202254437225137</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01593232503362858</v>
+        <v>-0.05052687935647131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1053752402979152</v>
+        <v>-0.02622565524420811</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.006025272029283137</v>
+        <v>-2.638859710766826e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1162256647131659</v>
+        <v>0.02156842937242058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0457020051154587</v>
+        <v>0.1111593222106727</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008092442451685508</v>
+        <v>-0.09385422311150657</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1066131859684052</v>
+        <v>0.05136298369211158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.1216231839998391</v>
+        <v>0.06217547433458897</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.05889363533053949</v>
+        <v>-0.2040283527519572</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0011004751380661</v>
+        <v>-0.2399863270597492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.1700957559145136</v>
+        <v>-0.150073250823658</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1902760771270562</v>
+        <v>0.1670624492661224</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1979080764301991</v>
+        <v>-0.2498371677575917</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.02019015472539007</v>
+        <v>-0.01114230966716615</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.1051313070594899</v>
+        <v>0.142277125699511</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2255623566867206</v>
+        <v>0.07370383671047322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0723829739109131</v>
+        <v>-0.03332463210036424</v>
       </c>
       <c r="B12" t="n">
-        <v>0.196461986961059</v>
+        <v>5.135361225006295e-05</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1144500456811398</v>
+        <v>-0.05743983263167129</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2405844033572513</v>
+        <v>-0.184939035514346</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1081341745460567</v>
+        <v>-0.3597277495546455</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1544804427359155</v>
+        <v>0.2513969532367255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.1087721297148089</v>
+        <v>0.02746488684596669</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2528929548619363</v>
+        <v>0.1367153419383917</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1087064844012539</v>
+        <v>0.2194325425664371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.001011193250341505</v>
+        <v>-0.230070913341288</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.004389656639624622</v>
+        <v>-0.05260964747362033</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.01064679631486314</v>
+        <v>-0.153372621983138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.1278503874264703</v>
+        <v>0.1670585726962796</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.05474033853186335</v>
+        <v>-0.01301063160472955</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01869900385454432</v>
+        <v>0.2126489633285145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.2250531389105157</v>
+        <v>0.06727219075566575</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.06568267820501411</v>
+        <v>-0.1358007263614504</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1229003324508724</v>
+        <v>-0.1150139003168238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0107248447666807</v>
+        <v>0.1444176934605021</v>
       </c>
       <c r="B18" t="n">
-        <v>-8.216804616361181e-06</v>
+        <v>0.09809563050557492</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06735891053444723</v>
+        <v>0.1631517206511029</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.203024637635016</v>
+        <v>2.433268121583628e-06</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1433388607458987</v>
+        <v>0.01915496154477709</v>
       </c>
       <c r="C19" t="n">
-        <v>0.133959459286084</v>
+        <v>0.0184746680931984</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.129953879553522</v>
+        <v>-0.1297139934795568</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2096243683693007</v>
+        <v>-0.006581600164854269</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.02614184438853027</v>
+        <v>-0.02681981709525279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.02889500406252479</v>
+        <v>-0.1018300870341078</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1238898536706083</v>
+        <v>0.03201903619142314</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1570929380792256</v>
+        <v>0.1771353674078319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.1217697083726979</v>
+        <v>0.02495475569670309</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1774395040596514</v>
+        <v>0.001069211243497564</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2399928370962979</v>
+        <v>0.1976712099183681</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.1035612506478312</v>
+        <v>-0.08454767800329951</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02838519750330683</v>
+        <v>0.009261340633696146</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.00499020859236424</v>
+        <v>-0.2007553378575565</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.1329847880027532</v>
+        <v>-0.2236005624988906</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.1485417355742632</v>
+        <v>0.0347044103747547</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1455455546971928</v>
+        <v>-0.15124669083574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.1912602684642669</v>
+        <v>0.05534744419660077</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1556515994059374</v>
+        <v>1.371190116694711e-07</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1117322969819125</v>
+        <v>-0.05630421890974836</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.02885660124503111</v>
+        <v>-0.02232069542584244</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.2186574203218374</v>
+        <v>0.1677790289519149</v>
       </c>
       <c r="C26" t="n">
-        <v>0.233757898951333</v>
+        <v>0.2429375122688997</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.01097818203993587</v>
+        <v>-0.02644507502498324</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04179569194321435</v>
+        <v>-0.03933668736768651</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1340802072032345</v>
+        <v>0.01809693957605862</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.01672519685002759</v>
+        <v>-0.1653090097022141</v>
       </c>
       <c r="B28" t="n">
-        <v>0.08120964443376873</v>
+        <v>0.1371997452589426</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07988014362458565</v>
+        <v>-0.1131119791557709</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.04323312104259219</v>
+        <v>0.09540903769741085</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.1334237099084442</v>
+        <v>-0.04025955595969373</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1897510122090456</v>
+        <v>-0.1534245520404338</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.08554490576103013</v>
+        <v>0.01343433655354511</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.05551895066147838</v>
+        <v>0.06127924413850545</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1982771881105537</v>
+        <v>-0.1828173654419744</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.06182795358388116</v>
+        <v>-0.07736052572419995</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.03520799100435661</v>
+        <v>0.06044954518113742</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.03643778470097583</v>
+        <v>-0.1111022697128011</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.2297281588866565</v>
+        <v>-0.08109776397736838</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1588388635057827</v>
+        <v>0.1423040419535966</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2215768806396208</v>
+        <v>-0.0331573778442236</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.2562660833153811</v>
+        <v>0.2464621394564514</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0045493004488093</v>
+        <v>-0.1474949700193148</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2254969417702486</v>
+        <v>0.07704179496977574</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.142304455057161</v>
+        <v>0.1437726344261472</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.07230737535050842</v>
+        <v>-0.02006536088860454</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.09356256657242167</v>
+        <v>0.116404305172908</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.04339059945496206</v>
+        <v>-0.1482515772353417</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0009684950753398205</v>
+        <v>-0.06632844140763883</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02328000029441792</v>
+        <v>0.002702450634627488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.1005805228991082</v>
+        <v>0.1782278246153031</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.1468893181206581</v>
+        <v>0.214261434262926</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1699317805083427</v>
+        <v>-0.1214422651403222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01880247865139576</v>
+        <v>0.03909423478775289</v>
       </c>
       <c r="B37" t="n">
-        <v>0.09235175384438585</v>
+        <v>-0.1826947686962</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.09857599270966265</v>
+        <v>-0.1798159953609385</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.1239754796518424</v>
+        <v>0.19130756565263</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.04457721295106053</v>
+        <v>0.1634530502804169</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0002960435473253412</v>
+        <v>0.1808484045415909</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.1886675675235801</v>
+        <v>-0.2498676893524058</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1041772940791862</v>
+        <v>-0.1794217696016732</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.127734451783682</v>
+        <v>-0.004852054004854627</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.05772823813044495</v>
+        <v>0.03780207390922723</v>
       </c>
       <c r="B40" t="n">
-        <v>0.02988229391979072</v>
+        <v>0.03750038898988391</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1384567082707876</v>
+        <v>0.1331196742375135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.2084192045829618</v>
+        <v>0.02999669380106324</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.1336432990745182</v>
+        <v>-1.1594544037359e-09</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0246653674656894</v>
+        <v>0.04634426236516492</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.02020480550302881</v>
+        <v>0.09347025384523854</v>
       </c>
       <c r="B42" t="n">
-        <v>0.07735137256004904</v>
+        <v>0.1272766601555258</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.09100078314940994</v>
+        <v>0.2193903417914745</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.09113002850320487</v>
+        <v>-0.07824503407069885</v>
       </c>
       <c r="B43" t="n">
-        <v>0.07148712315013216</v>
+        <v>-0.04497751584911249</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.06292321672851209</v>
+        <v>-0.003269877877377467</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.02571857271666509</v>
+        <v>-0.2525159934816192</v>
       </c>
       <c r="B44" t="n">
-        <v>0.04503879096083943</v>
+        <v>0.07603233417216856</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1466340670506451</v>
+        <v>0.09453446014523587</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.05104790690956946</v>
+        <v>-0.0373427443537987</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.00918235959045955</v>
+        <v>-0.09003612014297076</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05059832669159912</v>
+        <v>-0.1752153938858488</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.08011067483241256</v>
+        <v>0.1414581545020644</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.04642534948033446</v>
+        <v>-0.08062369756897879</v>
       </c>
       <c r="C46" t="n">
-        <v>0.09232594304557495</v>
+        <v>0.07863998692124557</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.1067471217500679</v>
+        <v>-0.1647816533366324</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.09511773280793479</v>
+        <v>-0.1281066816878335</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1159744662108056</v>
+        <v>-0.04352154284538177</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.0394700891374693</v>
+        <v>-2.896781157262524e-05</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1320666060637212</v>
+        <v>-1.737413104850103e-07</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1364115943562265</v>
+        <v>0.0148152751217871</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.2297220366950262</v>
+        <v>-0.07444459176383582</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.0281487475557416</v>
+        <v>-0.08543090020075161</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1340689961936511</v>
+        <v>-0.2464363991981848</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.01647333406046875</v>
+        <v>-0.03327703060193103</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.0001955141893396664</v>
+        <v>-0.2322744796323765</v>
       </c>
       <c r="C50" t="n">
-        <v>2.190299691958381e-05</v>
+        <v>0.0794409235366499</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.2189429139672559</v>
+        <v>0.01143651251512459</v>
       </c>
       <c r="B51" t="n">
-        <v>0.03115624484235803</v>
+        <v>-0.1753717811683722</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05932545978611051</v>
+        <v>0.06293879851798691</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.07987322674868037</v>
+        <v>-1.704705079973377e-08</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1975146325752735</v>
+        <v>8.888477803909276e-10</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1926229068517954</v>
+        <v>0.02605430087038541</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.01886147818447666</v>
+        <v>-0.1056364754241127</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1727676056433121</v>
+        <v>-0.1611859600018376</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.02330531935086945</v>
+        <v>0.125959238294419</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.2488108114787251</v>
+        <v>0.2543333667390671</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00200816646766832</v>
+        <v>-0.07365354651433273</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2151040599557803</v>
+        <v>0.1532546280673723</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.03998982626271385</v>
+        <v>0.178680625989139</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.2195565755097584</v>
+        <v>-0.03909358510397919</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03453013488473385</v>
+        <v>-0.1486387428235988</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.2019204145619183</v>
+        <v>0.2117651347204239</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.164007862186545</v>
+        <v>-0.09023603367284826</v>
       </c>
       <c r="C56" t="n">
-        <v>0.09883957680822511</v>
+        <v>0.1263001762128948</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.1172796646784442</v>
+        <v>-0.00137706508101583</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0359382327313208</v>
+        <v>-0.003773213360428377</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07544597997366245</v>
+        <v>-0.01114491837209789</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.1908750681116815</v>
+        <v>-0.2399951944676304</v>
       </c>
       <c r="B58" t="n">
-        <v>0.198042434351316</v>
+        <v>0.1978341071181848</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1466046910215337</v>
+        <v>0.02291656674429866</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1547820923380488</v>
+        <v>-0.2123611504606755</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1058439070900025</v>
+        <v>-0.0712575737633207</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1192713889191288</v>
+        <v>-0.004367232632328845</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.05123943232035304</v>
+        <v>-0.1386002446616662</v>
       </c>
       <c r="B60" t="n">
-        <v>0.08367136581023848</v>
+        <v>0.03789174767469971</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1762543670549381</v>
+        <v>0.1559318659670617</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.1192275857694841</v>
+        <v>-0.1823345464880695</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1973411321456436</v>
+        <v>-0.1734852305824533</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1353945205940151</v>
+        <v>-0.07428295342355531</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.1699930679446892</v>
+        <v>0.2069882897794769</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.0620288529364102</v>
+        <v>0.2190178559934546</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.04006193932764761</v>
+        <v>0.05877563387834943</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.01627785573845848</v>
+        <v>0.1436703239567055</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1289764658739906</v>
+        <v>0.1462749961431624</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1717907883545496</v>
+        <v>-0.1721449395452898</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.07001261666705887</v>
+        <v>0.2107196549661643</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.08045452098188738</v>
+        <v>0.1780321516872453</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2021529045912341</v>
+        <v>-0.05525374787008007</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.1049216843822858</v>
+        <v>0.1041054684442192</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1485896192124071</v>
+        <v>-0.06666534052170392</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2205833293676338</v>
+        <v>0.168275532405847</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.2433277520443399</v>
+        <v>0.06133224661380638</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.07384114310725094</v>
+        <v>-0.1638448692772425</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.09424063364035468</v>
+        <v>-0.1600366505323745</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.195156800834296</v>
+        <v>0.1014552775685852</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.1562267903481281</v>
+        <v>0.1830613634659801</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1097068188743901</v>
+        <v>-0.02248472355826482</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.121174766777664</v>
+        <v>-0.01501386442599697</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1507290853373384</v>
+        <v>-0.0007264523685968731</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2135946959257987</v>
+        <v>-3.715006087278302e-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.08334302118617631</v>
+        <v>-0.01912090275948138</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.2581251179644778</v>
+        <v>-0.0003563803655802619</v>
       </c>
       <c r="C69" t="n">
-        <v>0.151958829213733</v>
+        <v>-0.05009414771137968</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.004477960810100426</v>
+        <v>-0.1757530691078207</v>
       </c>
       <c r="B70" t="n">
-        <v>-2.197320111889579e-05</v>
+        <v>0.1138720202071363</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.02005496074224102</v>
+        <v>0.06143317566155349</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.01576233622807991</v>
+        <v>-0.04029633123615037</v>
       </c>
       <c r="B71" t="n">
-        <v>0.06677770723068467</v>
+        <v>0.1590304668206844</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1388864702672244</v>
+        <v>0.0814989269762926</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.1129289648883715</v>
+        <v>0.0007415806473831171</v>
       </c>
       <c r="B72" t="n">
-        <v>0.16464188383924</v>
+        <v>-0.04117600120360418</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.05901200565010573</v>
+        <v>-0.02047941011406672</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.2348094704859902</v>
+        <v>0.04471256785783986</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.1114723670297355</v>
+        <v>0.002357836901957493</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.01835019283818747</v>
+        <v>-0.1787760255425507</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.1970926472802825</v>
+        <v>-1.386061911342103e-05</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.1072566420325369</v>
+        <v>-0.01365500066859152</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1583690074781754</v>
+        <v>0.0424594773993556</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.118157415233733</v>
+        <v>0.1331852315138178</v>
       </c>
       <c r="B75" t="n">
-        <v>0.05139574683980898</v>
+        <v>-0.001527382643684396</v>
       </c>
       <c r="C75" t="n">
-        <v>0.02922714563046574</v>
+        <v>0.06859092412655034</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.023100869775905</v>
+        <v>0.01924911162023507</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1386898635161345</v>
+        <v>-0.02840006878469975</v>
       </c>
       <c r="C76" t="n">
-        <v>0.087277024649594</v>
+        <v>-7.311149674620883e-10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-0.04401983904827874</v>
+        <v>-0.1674887196869302</v>
       </c>
       <c r="B77" t="n">
-        <v>0.086687772736405</v>
+        <v>-0.01006266004075183</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02138188647231769</v>
+        <v>-0.1107900539586314</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.08644429181232634</v>
+        <v>0.1420222650924439</v>
       </c>
       <c r="B78" t="n">
-        <v>0.001425206084164916</v>
+        <v>0.1015274265602062</v>
       </c>
       <c r="C78" t="n">
-        <v>0.09507875753242066</v>
+        <v>0.02969799197398374</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.2091720149319188</v>
+        <v>0.222249063507189</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0911532220349018</v>
+        <v>-0.1790754580419825</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.2160040236918948</v>
+        <v>-0.1191638075155358</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.04764469311546721</v>
+        <v>0.1450939597776995</v>
       </c>
       <c r="B80" t="n">
-        <v>0.2019430219474124</v>
+        <v>-0.210150302796075</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.03926236730055557</v>
+        <v>0.1665835839358051</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-0.09750990019134227</v>
+        <v>0.196141250583483</v>
       </c>
       <c r="B81" t="n">
-        <v>0.08088276177368395</v>
+        <v>-0.1506108080576205</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.06210493876394452</v>
+        <v>-0.07004204443487949</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.2343968891506727</v>
+        <v>0.1228592326690544</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1634077345675888</v>
+        <v>-0.05857904246999839</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06677958083256491</v>
+        <v>0.03219603745436506</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.1093498775223214</v>
+        <v>0.004396281280908276</v>
       </c>
       <c r="B83" t="n">
-        <v>0.006347834953112774</v>
+        <v>0.1573652242321727</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1999465247490166</v>
+        <v>-0.1738586476845775</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.06644998924307427</v>
+        <v>0.01362564367071382</v>
       </c>
       <c r="B84" t="n">
-        <v>0.005932816888212494</v>
+        <v>-0.06707619723533374</v>
       </c>
       <c r="C84" t="n">
-        <v>0.03675993284921616</v>
+        <v>-0.03712558281879403</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.110178124964978</v>
+        <v>-0.1551467266743162</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.06996123737942163</v>
+        <v>0.08598538117786891</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.2214206171122779</v>
+        <v>-0.05262547186344953</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.1754845142392009</v>
+        <v>-0.1053896533648576</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.1231497565182557</v>
+        <v>0.04881100171900851</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1839656225704099</v>
+        <v>0.1302590214739902</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>6.719242340761736e-06</v>
+        <v>0.0532554592952522</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0103586647953789</v>
+        <v>0.04239089460352406</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.0425414566037965</v>
+        <v>-0.05532832611616927</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.0171605356661551</v>
+        <v>0.02295893800377187</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.01970312242098261</v>
+        <v>-0.1378471034943402</v>
       </c>
       <c r="C88" t="n">
-        <v>0.04824196168914659</v>
+        <v>-0.2429496332990593</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.08427212051307895</v>
+        <v>-0.004235859189085624</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.09509131116459488</v>
+        <v>-0.02380607329765884</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.05206058560216675</v>
+        <v>-0.003102904503249081</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.05709718909638181</v>
+        <v>0.09640689424635844</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.09803445673588952</v>
+        <v>-0.2066817114013982</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2289133322711678</v>
+        <v>-0.019299407929507</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.03322259904820656</v>
+        <v>0.05699211203410957</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.08139316641455654</v>
+        <v>-0.05405441872988088</v>
       </c>
       <c r="C91" t="n">
-        <v>0.008371812508733808</v>
+        <v>-0.1112080691700598</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.07026920724744055</v>
+        <v>0.001193448878790984</v>
       </c>
       <c r="B92" t="n">
-        <v>0.169904207058517</v>
+        <v>0.0001991106220996808</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.1230567584975749</v>
+        <v>-0.05017543151465655</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.001662657639571471</v>
+        <v>0.2105221173875327</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.05203858419365098</v>
+        <v>-0.1154957193864896</v>
       </c>
       <c r="C93" t="n">
-        <v>0.02116291832671592</v>
+        <v>-0.1647573466428967</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.1029049615245028</v>
+        <v>0.1502425331045847</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.1816140553461547</v>
+        <v>0.05962713129535158</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.03770220620845842</v>
+        <v>0.1168276846681174</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1065050824703524</v>
+        <v>0.1334529362565757</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.003446518637643252</v>
+        <v>-0.1082054256924771</v>
       </c>
       <c r="C95" t="n">
-        <v>0.03146023032126417</v>
+        <v>0.2206541846540901</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.001362700770733395</v>
+        <v>-0.01716048604977593</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.002145219606877759</v>
+        <v>0.07240782950387413</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.02810835869300101</v>
+        <v>-0.07784854623919671</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.1546481156479921</v>
+        <v>-0.06869136062221061</v>
       </c>
       <c r="B97" t="n">
-        <v>0.05382472326628216</v>
+        <v>-0.1734757039873694</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.06672087140914339</v>
+        <v>0.1108843289799769</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.1981537867959856</v>
+        <v>0.1384187753934788</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.1816369504616887</v>
+        <v>-0.05221164305029353</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1315972536813401</v>
+        <v>0.002597374859701565</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.1552566907962881</v>
+        <v>-0.001074285680928557</v>
       </c>
       <c r="B99" t="n">
-        <v>0.07632399674775397</v>
+        <v>0.1860820492367015</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.1876800628269002</v>
+        <v>0.1325712353597087</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.2075730890929521</v>
+        <v>-0.169450675218787</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.1887571300020568</v>
+        <v>-0.07349396851639595</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1544405175148515</v>
+        <v>0.02584251708890642</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.02933777715262977</v>
+        <v>-0.08535166223663999</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1626512485349868</v>
+        <v>0.003121104550445295</v>
       </c>
       <c r="C101" t="n">
-        <v>0.07198794821201651</v>
+        <v>0.03907044973735673</v>
       </c>
     </row>
   </sheetData>
